--- a/data/50001499 - EQ CHAPARRAL A.xlsx
+++ b/data/50001499 - EQ CHAPARRAL A.xlsx
@@ -10870,7 +10870,7 @@
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46125.908135590274</v>
+        <v>46188.18224864583</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>456</v>
@@ -10920,8 +10920,8 @@
       <c r="T158" s="6">
         <v>0</v>
       </c>
-      <c r="U158" s="10" t="s">
-        <v>128</v>
+      <c r="U158" s="12" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
